--- a/exports/test_en--ar_OMT_QE_scores_widn.xlsx
+++ b/exports/test_en--ar_OMT_QE_scores_widn.xlsx
@@ -513,12 +513,10 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.815865159034729</v>
-      </c>
+          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,9 +554,7 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0.8854202032089233</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,9 +596,7 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>0.9105714559555054</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,9 +638,7 @@
           <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>0.9270544648170471</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,9 +680,7 @@
           <t>كم عمرك؟</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>0.9216064214706421</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -725,16 +715,14 @@
         <v>0</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>0.9105714559555054</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -769,16 +757,14 @@
         <v>0</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>0.9270544648170471</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -813,16 +799,14 @@
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>كم عمرك؟</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0.9216064214706421</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -857,16 +841,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>0.9105714559555054</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/test_en--ar_OMT_QE_scores_widn.xlsx
+++ b/exports/test_en--ar_OMT_QE_scores_widn.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
+          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
+          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>

--- a/exports/test_en--ar_OMT_QE_scores_widn.xlsx
+++ b/exports/test_en--ar_OMT_QE_scores_widn.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>هذه كلمة بخط &lt;g1&gt;غامق&lt;/g1&gt;.</t>
+          <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -516,7 +516,9 @@
           <t>هذه كلمة بخط &lt;g1&gt;عريض&lt;/g1&gt;.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.815865159034729</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,7 +556,9 @@
           <t>هذه أفضل جملة لي حتى الآن.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.8854202032089233</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -596,7 +600,9 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.9105714559555054</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -638,7 +644,9 @@
           <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.9270544648170471</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -680,7 +688,9 @@
           <t>كم عمرك؟</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.9216064214706421</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -722,7 +732,9 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.9105714559555054</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,7 +776,9 @@
           <t>ما يلي موجه إلى فتاة:</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.9270544648170471</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -806,7 +820,9 @@
           <t>كم عمرك؟</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0.9216064214706421</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -848,7 +864,9 @@
           <t>هذه جملة مكررة.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.9105714559555054</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
